--- a/assets/roadmap/Catalogo_Soluciones_MM_Agro_Pymes_v2-Chile.xlsx
+++ b/assets/roadmap/Catalogo_Soluciones_MM_Agro_Pymes_v2-Chile.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Catalogo_Soluciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuentes" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Conteo_por_KPI" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Catalogo_Soluciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuentes" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Resumen" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Conteo_por_KPI" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -2147,7 +2147,7 @@
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -4317,7 +4317,7 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7030,7 +7030,7 @@
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -7191,7 +7191,7 @@
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
@@ -7352,7 +7352,7 @@
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
@@ -7513,7 +7513,7 @@
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
@@ -8288,7 +8288,7 @@
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
@@ -8443,7 +8443,7 @@
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="T53" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U53" s="2" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="T54" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U54" s="2" t="inlineStr">
@@ -9063,7 +9063,7 @@
       </c>
       <c r="T55" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U55" s="2" t="inlineStr">
@@ -9218,7 +9218,7 @@
       </c>
       <c r="T56" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U56" s="2" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="T57" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U57" s="2" t="inlineStr">
@@ -9533,7 +9533,7 @@
       </c>
       <c r="T58" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U58" s="2" t="inlineStr">
@@ -9693,7 +9693,7 @@
       </c>
       <c r="T59" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U59" s="2" t="inlineStr">
@@ -9854,7 +9854,7 @@
       </c>
       <c r="T60" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U60" s="2" t="inlineStr">
@@ -10015,7 +10015,7 @@
       </c>
       <c r="T61" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U61" s="2" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="T70" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U70" s="2" t="inlineStr">
@@ -11589,7 +11589,7 @@
       </c>
       <c r="T71" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U71" s="2" t="inlineStr">
@@ -11744,7 +11744,7 @@
       </c>
       <c r="T72" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U72" s="2" t="inlineStr">
@@ -11899,7 +11899,7 @@
       </c>
       <c r="T73" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U73" s="2" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="T74" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U74" s="2" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>https://liquidacion.pcfactory.cl/listaPrecios.pdf?t=20250820023904</t>
+          <t>https://www.pcfactory.cl/search?query=all%20in%20one</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
@@ -12209,7 +12209,7 @@
       </c>
       <c r="T75" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U75" s="2" t="inlineStr">
@@ -12364,7 +12364,7 @@
       </c>
       <c r="T76" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U76" s="2" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>https://liquidacion.pcfactory.cl/listaPrecios.pdf?t=20250820023904</t>
+          <t>https://www.pcfactory.cl/search?query=all%20in%20one</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
@@ -12519,7 +12519,7 @@
       </c>
       <c r="T77" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U77" s="2" t="inlineStr">
@@ -15798,7 +15798,7 @@
       </c>
       <c r="T98" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U98" s="2" t="inlineStr">
@@ -15953,7 +15953,7 @@
       </c>
       <c r="T99" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U99" s="2" t="inlineStr">
@@ -16108,7 +16108,7 @@
       </c>
       <c r="T100" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U100" s="2" t="inlineStr">
@@ -16263,7 +16263,7 @@
       </c>
       <c r="T101" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U101" s="2" t="inlineStr">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="T102" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U102" s="2" t="inlineStr">
@@ -16573,7 +16573,7 @@
       </c>
       <c r="T103" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U103" s="2" t="inlineStr">
@@ -18592,7 +18592,7 @@
       </c>
       <c r="T116" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U116" s="2" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="T117" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U117" s="2" t="inlineStr">
@@ -18902,7 +18902,7 @@
       </c>
       <c r="T118" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U118" s="2" t="inlineStr">
@@ -19057,7 +19057,7 @@
       </c>
       <c r="T119" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U119" s="2" t="inlineStr">
@@ -19212,7 +19212,7 @@
       </c>
       <c r="T120" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U120" s="2" t="inlineStr">
@@ -19367,7 +19367,7 @@
       </c>
       <c r="T121" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://www.defontana.com/cl/erp/software-punto-de-venta-pos-pro/</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://www.defontana.com/cl/pos-tivendo/</t>
         </is>
       </c>
       <c r="U121" s="2" t="inlineStr">
@@ -19522,7 +19522,7 @@
       </c>
       <c r="T122" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U122" s="2" t="inlineStr">
@@ -19677,7 +19677,7 @@
       </c>
       <c r="T123" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U123" s="2" t="inlineStr">
@@ -19832,7 +19832,7 @@
       </c>
       <c r="T124" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U124" s="2" t="inlineStr">
@@ -19987,7 +19987,7 @@
       </c>
       <c r="T125" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U125" s="2" t="inlineStr">
@@ -20142,7 +20142,7 @@
       </c>
       <c r="T126" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U126" s="2" t="inlineStr">
@@ -20297,7 +20297,7 @@
       </c>
       <c r="T127" s="2" t="inlineStr">
         <is>
-          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.agromet.cl/que-es-agromet | https://www.inia.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U127" s="2" t="inlineStr">
@@ -23356,7 +23356,7 @@
       </c>
       <c r="T146" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U146" s="2" t="inlineStr">
@@ -23517,7 +23517,7 @@
       </c>
       <c r="T147" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U147" s="2" t="inlineStr">
@@ -23678,7 +23678,7 @@
       </c>
       <c r="T148" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U148" s="2" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="T149" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U149" s="2" t="inlineStr">
@@ -24000,7 +24000,7 @@
       </c>
       <c r="T150" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U150" s="2" t="inlineStr">
@@ -24161,7 +24161,7 @@
       </c>
       <c r="T151" s="2" t="inlineStr">
         <is>
-          <t>https://www.nubox.com/software/remuneraciones/</t>
+          <t>https://www.nubox.com/software-de-remuneraciones/</t>
         </is>
       </c>
       <c r="U151" s="2" t="inlineStr">
@@ -25246,7 +25246,7 @@
       </c>
       <c r="T158" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U158" s="2" t="inlineStr">
@@ -25401,7 +25401,7 @@
       </c>
       <c r="T159" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U159" s="2" t="inlineStr">
@@ -25556,7 +25556,7 @@
       </c>
       <c r="T160" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U160" s="2" t="inlineStr">
@@ -25711,7 +25711,7 @@
       </c>
       <c r="T161" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U161" s="2" t="inlineStr">
@@ -25866,7 +25866,7 @@
       </c>
       <c r="T162" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U162" s="2" t="inlineStr">
@@ -26021,7 +26021,7 @@
       </c>
       <c r="T163" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U163" s="2" t="inlineStr">
@@ -26176,7 +26176,7 @@
       </c>
       <c r="T164" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U164" s="2" t="inlineStr">
@@ -26331,7 +26331,7 @@
       </c>
       <c r="T165" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U165" s="2" t="inlineStr">
@@ -26486,7 +26486,7 @@
       </c>
       <c r="T166" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U166" s="2" t="inlineStr">
@@ -26641,7 +26641,7 @@
       </c>
       <c r="T167" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U167" s="2" t="inlineStr">
@@ -26796,7 +26796,7 @@
       </c>
       <c r="T168" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U168" s="2" t="inlineStr">
@@ -26951,7 +26951,7 @@
       </c>
       <c r="T169" s="2" t="inlineStr">
         <is>
-          <t>https://khipu.com/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://khipu.com/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U169" s="2" t="inlineStr">
@@ -27111,7 +27111,7 @@
       </c>
       <c r="T170" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U170" s="2" t="inlineStr">
@@ -27271,7 +27271,7 @@
       </c>
       <c r="T171" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U171" s="2" t="inlineStr">
@@ -27432,7 +27432,7 @@
       </c>
       <c r="T172" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U172" s="2" t="inlineStr">
@@ -27593,7 +27593,7 @@
       </c>
       <c r="T173" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U173" s="2" t="inlineStr">
@@ -27754,7 +27754,7 @@
       </c>
       <c r="T174" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U174" s="2" t="inlineStr">
@@ -27915,7 +27915,7 @@
       </c>
       <c r="T175" s="2" t="inlineStr">
         <is>
-          <t>https://jumpseller.com/enterprise/ | https://jumpseller.com/pricing/</t>
+          <t>https://jumpseller.com/enterprise/ | https://jumpseller.cl/sign-up-main/</t>
         </is>
       </c>
       <c r="U175" s="2" t="inlineStr">
@@ -29954,7 +29954,7 @@
       </c>
       <c r="T188" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U188" s="2" t="inlineStr">
@@ -30109,7 +30109,7 @@
       </c>
       <c r="T189" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U189" s="2" t="inlineStr">
@@ -30264,7 +30264,7 @@
       </c>
       <c r="T190" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U190" s="2" t="inlineStr">
@@ -30419,7 +30419,7 @@
       </c>
       <c r="T191" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U191" s="2" t="inlineStr">
@@ -30574,7 +30574,7 @@
       </c>
       <c r="T192" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U192" s="2" t="inlineStr">
@@ -30729,7 +30729,7 @@
       </c>
       <c r="T193" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/ | https://sence.gob.cl/personas/cursos-en-linea</t>
+          <t>https://www.defontana.com/cl/valorpyme | https://sence.gob.cl/personas/cursos-en-linea</t>
         </is>
       </c>
       <c r="U193" s="2" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="T194" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U194" s="2" t="inlineStr">
@@ -31039,7 +31039,7 @@
       </c>
       <c r="T195" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U195" s="2" t="inlineStr">
@@ -31194,7 +31194,7 @@
       </c>
       <c r="T196" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U196" s="2" t="inlineStr">
@@ -31349,7 +31349,7 @@
       </c>
       <c r="T197" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U197" s="2" t="inlineStr">
@@ -31504,7 +31504,7 @@
       </c>
       <c r="T198" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U198" s="2" t="inlineStr">
@@ -31659,7 +31659,7 @@
       </c>
       <c r="T199" s="2" t="inlineStr">
         <is>
-          <t>https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U199" s="2" t="inlineStr">
@@ -31814,7 +31814,7 @@
       </c>
       <c r="T200" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U200" s="2" t="inlineStr">
@@ -31834,7 +31834,7 @@
       </c>
       <c r="X200" s="2" t="inlineStr">
         <is>
-          <t>https://liquidacion.pcfactory.cl/listaPrecios.pdf?t=20250820023904</t>
+          <t>https://www.pcfactory.cl/search?query=all%20in%20one</t>
         </is>
       </c>
       <c r="Y200" s="2" t="inlineStr">
@@ -31969,7 +31969,7 @@
       </c>
       <c r="T201" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U201" s="2" t="inlineStr">
@@ -32124,7 +32124,7 @@
       </c>
       <c r="T202" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U202" s="2" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="X202" s="2" t="inlineStr">
         <is>
-          <t>https://liquidacion.pcfactory.cl/listaPrecios.pdf?t=20250820023904</t>
+          <t>https://www.pcfactory.cl/search?query=all%20in%20one</t>
         </is>
       </c>
       <c r="Y202" s="2" t="inlineStr">
@@ -32279,7 +32279,7 @@
       </c>
       <c r="T203" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U203" s="2" t="inlineStr">
@@ -32434,7 +32434,7 @@
       </c>
       <c r="T204" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U204" s="2" t="inlineStr">
@@ -32454,7 +32454,7 @@
       </c>
       <c r="X204" s="2" t="inlineStr">
         <is>
-          <t>https://liquidacion.pcfactory.cl/listaPrecios.pdf?t=20250820023904</t>
+          <t>https://www.pcfactory.cl/search?query=all%20in%20one</t>
         </is>
       </c>
       <c r="Y204" s="2" t="inlineStr">
@@ -32589,7 +32589,7 @@
       </c>
       <c r="T205" s="2" t="inlineStr">
         <is>
-          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/erp/erp-valor-pyme/</t>
+          <t>https://www.pcfactory.cl/ | https://www.defontana.com/cl/valorpyme</t>
         </is>
       </c>
       <c r="U205" s="2" t="inlineStr">
@@ -35406,7 +35406,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://liquidacion.pcfactory.cl/listaPrecios.pdf?t=20250820023904</t>
+          <t>https://www.pcfactory.cl/search?query=all%20in%20one</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -35433,7 +35433,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://liquidacion.pcfactory.cl/listaPrecios.pdf?t=20250820023904</t>
+          <t>https://www.pcfactory.cl/search?query=all%20in%20one</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
